--- a/artfynd/A 2968-2022 artfynd.xlsx
+++ b/artfynd/A 2968-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2968-2022 artfynd.xlsx
+++ b/artfynd/A 2968-2022 artfynd.xlsx
@@ -675,52 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91791529</v>
+        <v>91791064</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eskilstuna, Srm</t>
+          <t>Sågarsvedet, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597612.0532117792</v>
+        <v>597583</v>
       </c>
       <c r="R2" t="n">
-        <v>6565953.269457904</v>
+        <v>6566054</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +753,14 @@
           <t>2021-03-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-03-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,19 +783,18 @@
           <t>Fredrik Enoksson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91791064</v>
+        <v>91791409</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,33 +802,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597583.2950076984</v>
+        <v>597618</v>
       </c>
       <c r="R3" t="n">
-        <v>6566054.440632049</v>
+        <v>6566042</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,24 +860,9 @@
           <t>2021-03-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91791409</v>
+        <v>91791355</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,35 +904,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sågarsvedet, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597617.9979559327</v>
+        <v>597687</v>
       </c>
       <c r="R4" t="n">
-        <v>6566041.504062666</v>
+        <v>6566104</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,19 +968,9 @@
           <t>2021-03-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,15 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91791355</v>
+        <v>91791529</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,41 +1012,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sågarsvedet, Srm</t>
+          <t>Eskilstuna, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597687.1955536117</v>
+        <v>597612</v>
       </c>
       <c r="R5" t="n">
-        <v>6566103.707126955</v>
+        <v>6565953</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,19 +1071,9 @@
           <t>2021-03-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,11 +1096,7 @@
           <t>Fredrik Enoksson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Lst D inventering sandbarrskogar</t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2968-2022 artfynd.xlsx
+++ b/artfynd/A 2968-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91791064</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91791409</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91791355</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,8 +1117,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91791529</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>